--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230601_20231201.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230601_20231201.xlsx
@@ -1009,37 +1009,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.87096774193549</v>
+        <v>60.48387096774194</v>
       </c>
       <c r="C14" t="n">
-        <v>39.51612903225806</v>
+        <v>38.70967741935484</v>
       </c>
       <c r="D14" t="n">
-        <v>81.35459624211134</v>
+        <v>79.14668270494339</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INE257A01026</t>
+          <t>INE103A01014</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.35483870967742</v>
+        <v>-21.7741935483871</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
         <v>66</v>
       </c>
       <c r="J14" t="n">
-        <v>170.45</v>
+        <v>121.3</v>
       </c>
       <c r="K14" t="n">
         <v>13</v>
@@ -1053,37 +1053,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60.48387096774194</v>
+        <v>58.87096774193549</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70967741935484</v>
+        <v>39.51612903225806</v>
       </c>
       <c r="D15" t="n">
-        <v>79.14668270494339</v>
+        <v>81.35459624211134</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE103A01014</t>
+          <t>INE257A01026</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>-21.7741935483871</v>
+        <v>-19.35483870967742</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
         <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>121.3</v>
+        <v>170.45</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
